--- a/public/Template-Data-PKPRB.xlsx
+++ b/public/Template-Data-PKPRB.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
@@ -1122,6 +1122,27 @@
       <c r="A61" t="inlineStr">
         <is>
           <t>28 Agu 2026 — 05 opsi 1: koropleth Bahaya/Keselarasan = IRBI 2025 komposit saja. Filter jenis bahaya hanya mengubah bobot prodi, kecocokan pusat, dan filter historis. 04 layanan ditunda; kepakaran = flag pkm di 03.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>28 Agu 2026 — 05 kolom gempa diganti rata-rata kabupaten IRBI 2025 (514 kab, hlm. 230–245). Bukan max. Kolom tsunami–karhutla masih prototipe. Pewarnaan peta tetap komposit sampai ancaman lain terisi dan kode diaktifkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>28 Agu 2026 — 05 kolom tsunami = rata-rata kabupaten IRBI 2025 (hlm. 248–256, ~271 kab). Provinsi tanpa baris (Jambi, Riau, Babel, Kepri, DIY, Kalbar, Papua Pegunungan) = 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>28 Agu 2026 — 05 banjir/gunungapi/karhutla/longsor/likuefaksi = rata-rata kabupaten IRBI 2025. Pewarnaan peta masih komposit. Likuefaksi 514 kab; gunung api hanya ~130 kab (20 provinsi = 0).</t>
         </is>
       </c>
     </row>
@@ -21702,25 +21723,25 @@
         <v>192.75</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>90</v>
+        <v>22.23</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>96</v>
+        <v>22.61</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>52</v>
+        <v>19.94</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>58</v>
+        <v>21.24</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>72</v>
+        <v>16.17</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>18</v>
+        <v>10.88</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>22</v>
+        <v>20.94</v>
       </c>
       <c r="O2" s="6" t="inlineStr"/>
       <c r="P2" s="6" t="inlineStr">
@@ -21730,7 +21751,7 @@
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=192.75 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=22.23 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=22.61 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=19.94; longsor=21.24; likuefaksi=16.17; gunungapi=10.88; karhutla=20.94 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -21777,25 +21798,25 @@
         <v>162.25</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>62</v>
+        <v>22.24</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>48</v>
+        <v>16.45</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>58</v>
+        <v>14.6</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>50</v>
+        <v>23.52</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>28</v>
+        <v>18.26</v>
       </c>
       <c r="M3" s="6" t="n">
-        <v>35</v>
+        <v>18.32</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>30</v>
+        <v>20.07</v>
       </c>
       <c r="O3" s="6" t="inlineStr"/>
       <c r="P3" s="6" t="inlineStr">
@@ -21805,7 +21826,7 @@
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=162.25. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=22.24 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=16.45 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=14.6; longsor=23.52; likuefaksi=18.26; gunungapi=18.32; karhutla=20.07 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -21852,25 +21873,25 @@
         <v>176.82</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>88</v>
+        <v>24.16</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>90</v>
+        <v>21.24</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>48</v>
+        <v>14.04</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>70</v>
+        <v>20.2</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>60</v>
+        <v>19.17</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>40</v>
+        <v>17.18</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>18</v>
+        <v>19.48</v>
       </c>
       <c r="O4" s="6" t="inlineStr"/>
       <c r="P4" s="6" t="inlineStr">
@@ -21880,7 +21901,7 @@
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=176.82. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=24.16 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=21.24 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=14.04; longsor=20.2; likuefaksi=19.17; gunungapi=17.18; karhutla=19.48 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -21927,25 +21948,25 @@
         <v>118.15</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>28</v>
+        <v>7.34</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>55</v>
+        <v>15.52</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>22</v>
+        <v>17.17</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>12</v>
+        <v>14.32</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>95</v>
+        <v>23.19</v>
       </c>
       <c r="O5" s="6" t="inlineStr"/>
       <c r="P5" s="6" t="inlineStr">
@@ -21955,7 +21976,7 @@
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=118.15 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=7.34 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=0.0 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=15.52; longsor=17.17; likuefaksi=14.32; gunungapi=0.0; karhutla=23.19 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -22002,25 +22023,25 @@
         <v>132.45</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>32</v>
+        <v>14.46</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>60</v>
+        <v>17.47</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>35</v>
+        <v>20.6</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>15</v>
+        <v>11.54</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>15</v>
+        <v>26.4</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="O6" s="6" t="inlineStr"/>
       <c r="P6" s="6" t="inlineStr">
@@ -22030,7 +22051,7 @@
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=132.45 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=14.46 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=0.0 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=17.47; longsor=20.6; likuefaksi=11.54; gunungapi=26.4; karhutla=24.0 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -22077,25 +22098,25 @@
         <v>139.67</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>30</v>
+        <v>13.42</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>20</v>
+        <v>1.4</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>62</v>
+        <v>14.85</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>28</v>
+        <v>18.05</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>14</v>
+        <v>15.93</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>90</v>
+        <v>20.28</v>
       </c>
       <c r="O7" s="6" t="inlineStr"/>
       <c r="P7" s="6" t="inlineStr">
@@ -22105,7 +22126,7 @@
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=139.67 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=13.42 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=1.4 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=14.85; longsor=18.05; likuefaksi=15.93; gunungapi=12.5; karhutla=20.28 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -22152,25 +22173,25 @@
         <v>183.6</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>86</v>
+        <v>21.62</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>80</v>
+        <v>22.59</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>40</v>
+        <v>14.32</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>55</v>
+        <v>20.27</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>50</v>
+        <v>15.08</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>30</v>
+        <v>17.71</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>20</v>
+        <v>18.28</v>
       </c>
       <c r="O8" s="6" t="inlineStr"/>
       <c r="P8" s="6" t="inlineStr">
@@ -22180,7 +22201,7 @@
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=183.6 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=21.62 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=22.59 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=14.32; longsor=20.27; likuefaksi=15.08; gunungapi=17.71; karhutla=18.28 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -22227,25 +22248,25 @@
         <v>124.59</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>78</v>
+        <v>12.86</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>82</v>
+        <v>12.47</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>58</v>
+        <v>10.21</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>48</v>
+        <v>15.62</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>40</v>
+        <v>10.71</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>25</v>
+        <v>19.22</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>35</v>
+        <v>14.76</v>
       </c>
       <c r="O9" s="6" t="inlineStr"/>
       <c r="P9" s="6" t="inlineStr">
@@ -22255,7 +22276,7 @@
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=124.59 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=12.86 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=12.47 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=10.21; longsor=15.62; likuefaksi=10.71; gunungapi=19.22; karhutla=14.76 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -22302,25 +22323,25 @@
         <v>113.13</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>22</v>
+        <v>1.41</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>48</v>
+        <v>12.88</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>18</v>
+        <v>16.47</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>10</v>
+        <v>10.16</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>40</v>
+        <v>17.61</v>
       </c>
       <c r="O10" s="6" t="inlineStr"/>
       <c r="P10" s="6" t="inlineStr">
@@ -22330,7 +22351,7 @@
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=113.13. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=1.41 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=0.0 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=12.88; longsor=16.47; likuefaksi=10.16; gunungapi=0.0; karhutla=17.61 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -22377,25 +22398,25 @@
         <v>132.68</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>25</v>
+        <v>2.34</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>42</v>
+        <v>16.58</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>12</v>
+        <v>20.51</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>8</v>
+        <v>14.61</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>22</v>
+        <v>22.59</v>
       </c>
       <c r="O11" s="6" t="inlineStr"/>
       <c r="P11" s="6" t="inlineStr">
@@ -22405,7 +22426,7 @@
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=132.68 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=2.34 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=0.0 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=16.58; longsor=20.51; likuefaksi=14.61; gunungapi=0.0; karhutla=22.59 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -22452,25 +22473,25 @@
         <v>57.58</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>35</v>
+        <v>17.49</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>20</v>
+        <v>2.41</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>75</v>
+        <v>10.93</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>22</v>
+        <v>8.82</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O12" s="6" t="inlineStr"/>
       <c r="P12" s="6" t="inlineStr">
@@ -22480,7 +22501,7 @@
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=57.58 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=17.49 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=2.41 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=10.93; longsor=0.0; likuefaksi=8.82; gunungapi=0.0; karhutla=0.0 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -22527,25 +22548,25 @@
         <v>106.02</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>72</v>
+        <v>15.71</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>70</v>
+        <v>11.26</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>80</v>
+        <v>10.8</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>78</v>
+        <v>13.67</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>40</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>45</v>
+        <v>9.4</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>18</v>
+        <v>12.17</v>
       </c>
       <c r="O13" s="6" t="inlineStr"/>
       <c r="P13" s="6" t="inlineStr">
@@ -22555,7 +22576,7 @@
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=106.02 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=15.71 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=11.26 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=10.8; longsor=13.67; likuefaksi=9.11; gunungapi=9.4; karhutla=12.17 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -22602,25 +22623,25 @@
         <v>92.37</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>68</v>
+        <v>9.48</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>45</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>75</v>
+        <v>9.25</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>80</v>
+        <v>11.9</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>35</v>
+        <v>8.67</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>70</v>
+        <v>9.51</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>15</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="O14" s="6" t="inlineStr"/>
       <c r="P14" s="6" t="inlineStr">
@@ -22630,7 +22651,7 @@
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=92.37 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=9.48 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=9.95 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=9.25; longsor=11.9; likuefaksi=8.67; gunungapi=9.51; karhutla=9.79 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -22677,25 +22698,25 @@
         <v>88.91</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>85</v>
+        <v>12.86</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>48</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>65</v>
+        <v>10.05</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>70</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>8</v>
+        <v>6.36</v>
       </c>
       <c r="O15" s="6" t="inlineStr"/>
       <c r="P15" s="6" t="inlineStr">
@@ -22705,7 +22726,7 @@
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=88.91 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=12.86 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=0.0 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=8.78; longsor=10.05; likuefaksi=8.53; gunungapi=0.0; karhutla=6.36 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
@@ -22752,25 +22773,25 @@
         <v>108.36</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>58</v>
+        <v>14.85</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>40</v>
+        <v>6.77</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>72</v>
+        <v>11.69</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>62</v>
+        <v>12.79</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>28</v>
+        <v>11.44</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>80</v>
+        <v>10.43</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>20</v>
+        <v>11.66</v>
       </c>
       <c r="O16" s="6" t="inlineStr"/>
       <c r="P16" s="6" t="inlineStr">
@@ -22780,7 +22801,7 @@
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=108.36. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=14.85 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=6.77 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=11.69; longsor=12.79; likuefaksi=11.44; gunungapi=10.43; karhutla=11.66 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
@@ -22827,25 +22848,25 @@
         <v>103.58</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>70</v>
+        <v>15.42</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>75</v>
+        <v>10.04</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>68</v>
+        <v>10.54</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>50</v>
+        <v>13.06</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>32</v>
+        <v>10.01</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>30</v>
+        <v>13.46</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="O17" s="6" t="inlineStr"/>
       <c r="P17" s="6" t="inlineStr">
@@ -22855,7 +22876,7 @@
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=103.58 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=15.42 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=10.04 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=10.54; longsor=13.06; likuefaksi=10.01; gunungapi=13.46; karhutla=8.5 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -22902,25 +22923,25 @@
         <v>123.35</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>74</v>
+        <v>14.38</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>55</v>
+        <v>15.57</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>42</v>
+        <v>10.04</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>40</v>
+        <v>13.48</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>30</v>
+        <v>10.12</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>78</v>
+        <v>10.49</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>6</v>
+        <v>11.11</v>
       </c>
       <c r="O18" s="6" t="inlineStr"/>
       <c r="P18" s="6" t="inlineStr">
@@ -22930,7 +22951,7 @@
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=123.35 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=14.38 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=15.57 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=10.04; longsor=13.48; likuefaksi=10.12; gunungapi=10.49; karhutla=11.11 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -22977,25 +22998,25 @@
         <v>156.02</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>88</v>
+        <v>16.85</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>50</v>
+        <v>17.35</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>45</v>
+        <v>9.65</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>48</v>
+        <v>15.74</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>75</v>
+        <v>15.81</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>72</v>
+        <v>7.99</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>10</v>
+        <v>15.02</v>
       </c>
       <c r="O19" s="6" t="inlineStr"/>
       <c r="P19" s="6" t="inlineStr">
@@ -23005,7 +23026,7 @@
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=156.02 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=16.85 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=17.35 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=9.65; longsor=15.74; likuefaksi=15.81; gunungapi=7.99; karhutla=15.02 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -23052,25 +23073,25 @@
         <v>197.43</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>80</v>
+        <v>21.15</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>70</v>
+        <v>20.93</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>52</v>
+        <v>10.43</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>55</v>
+        <v>20.76</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>30</v>
+        <v>15.97</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>85</v>
+        <v>18.08</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>12</v>
+        <v>19.13</v>
       </c>
       <c r="O20" s="6" t="inlineStr"/>
       <c r="P20" s="6" t="inlineStr">
@@ -23080,7 +23101,7 @@
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=197.43 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=21.15 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=20.93 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=10.43; longsor=20.76; likuefaksi=15.97; gunungapi=18.08; karhutla=19.13 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -23127,25 +23148,25 @@
         <v>113.32</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>22</v>
+        <v>1.31</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>70</v>
+        <v>13.46</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>30</v>
+        <v>18.55</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>8</v>
+        <v>13.33</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>85</v>
+        <v>18.17</v>
       </c>
       <c r="O21" s="6" t="inlineStr"/>
       <c r="P21" s="6" t="inlineStr">
@@ -23155,7 +23176,7 @@
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=113.32. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=1.31 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=0.0 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=13.46; longsor=18.55; likuefaksi=13.33; gunungapi=0.0; karhutla=18.17 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -23202,25 +23223,25 @@
         <v>104.76</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>18</v>
+        <v>1.17</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>8</v>
+        <v>2.41</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>65</v>
+        <v>11.94</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>22</v>
+        <v>12.99</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>6</v>
+        <v>12.83</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>92</v>
+        <v>18.37</v>
       </c>
       <c r="O22" s="6" t="inlineStr"/>
       <c r="P22" s="6" t="inlineStr">
@@ -23230,7 +23251,7 @@
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=104.76 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=1.17 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=2.41 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=11.94; longsor=12.99; likuefaksi=12.83; gunungapi=0.0; karhutla=18.37 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -23277,25 +23298,25 @@
         <v>83.68000000000001</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>24</v>
+        <v>1.24</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>78</v>
+        <v>11.1</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>40</v>
+        <v>16.69</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>10</v>
+        <v>11.08</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>88</v>
+        <v>15.21</v>
       </c>
       <c r="O23" s="6" t="inlineStr"/>
       <c r="P23" s="6" t="inlineStr">
@@ -23305,7 +23326,7 @@
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=83.68 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=1.24 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=1.0 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=11.1; longsor=16.69; likuefaksi=11.08; gunungapi=0.0; karhutla=15.21 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -23352,25 +23373,25 @@
         <v>117.73</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>30</v>
+        <v>4.34</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>20</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>58</v>
+        <v>10.57</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>28</v>
+        <v>12.81</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>12</v>
+        <v>11.95</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>70</v>
+        <v>15.64</v>
       </c>
       <c r="O24" s="6" t="inlineStr"/>
       <c r="P24" s="6" t="inlineStr">
@@ -23380,7 +23401,7 @@
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=117.73 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=4.34 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=8.88 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=10.57; longsor=12.81; likuefaksi=11.95; gunungapi=0.0; karhutla=15.64 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -23427,25 +23448,25 @@
         <v>121.35</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>28</v>
+        <v>1.24</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>22</v>
+        <v>13.47</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>50</v>
+        <v>10.08</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>25</v>
+        <v>11.34</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>10</v>
+        <v>11.02</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>55</v>
+        <v>14.94</v>
       </c>
       <c r="O25" s="6" t="inlineStr"/>
       <c r="P25" s="6" t="inlineStr">
@@ -23455,7 +23476,7 @@
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=121.35 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=1.24 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=13.47 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=10.08; longsor=11.34; likuefaksi=11.02; gunungapi=0.0; karhutla=14.94 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -23502,25 +23523,25 @@
         <v>176.82</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>82</v>
+        <v>19.23</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>70</v>
+        <v>21.02</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>48</v>
+        <v>15.09</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>50</v>
+        <v>19.23</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>35</v>
+        <v>14.82</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>80</v>
+        <v>15.52</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>8</v>
+        <v>18.24</v>
       </c>
       <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="6" t="inlineStr">
@@ -23530,7 +23551,7 @@
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=176.82 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=19.23 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=21.02 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=15.09; longsor=19.23; likuefaksi=14.82; gunungapi=15.52; karhutla=18.24 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -23577,25 +23598,25 @@
         <v>195.78</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>92</v>
+        <v>21.79</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>85</v>
+        <v>21.53</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>50</v>
+        <v>14.69</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>55</v>
+        <v>21.79</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>95</v>
+        <v>15.44</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>30</v>
+        <v>26.4</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>12</v>
+        <v>20.8</v>
       </c>
       <c r="O27" s="6" t="inlineStr"/>
       <c r="P27" s="6" t="inlineStr">
@@ -23605,7 +23626,7 @@
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=195.78 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=21.79 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=21.53 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=14.69; longsor=21.79; likuefaksi=15.44; gunungapi=26.4; karhutla=20.8 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -23652,25 +23673,25 @@
         <v>196.55</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>70</v>
+        <v>4.92</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>65</v>
+        <v>14.9</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>72</v>
+        <v>15.69</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>75</v>
+        <v>21.61</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>40</v>
+        <v>14.88</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>18</v>
+        <v>21.12</v>
       </c>
       <c r="O28" s="6" t="inlineStr"/>
       <c r="P28" s="6" t="inlineStr">
@@ -23680,7 +23701,7 @@
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=196.55 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=4.92 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=14.9 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=15.69; longsor=21.61; likuefaksi=14.88; gunungapi=0.0; karhutla=21.12 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -23727,25 +23748,25 @@
         <v>178.9</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>60</v>
+        <v>24.99</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>55</v>
+        <v>17.17</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>48</v>
+        <v>19.95</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>30</v>
+        <v>17.15</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>15</v>
+        <v>23.8</v>
       </c>
       <c r="O29" s="6" t="inlineStr"/>
       <c r="P29" s="6" t="inlineStr">
@@ -23755,7 +23776,7 @@
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=178.9. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=8.38 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=24.99 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=17.17; longsor=19.95; likuefaksi=17.15; gunungapi=0.0; karhutla=23.8 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -23802,25 +23823,25 @@
         <v>164.37</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>78</v>
+        <v>17.49</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>45</v>
+        <v>17.86</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>60</v>
+        <v>12.85</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>52</v>
+        <v>14.45</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>28</v>
+        <v>12.57</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>10</v>
+        <v>15.8</v>
       </c>
       <c r="O30" s="6" t="inlineStr"/>
       <c r="P30" s="6" t="inlineStr">
@@ -23830,7 +23851,7 @@
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=164.37 kelas Sedang. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=17.49 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=17.86 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=12.85; longsor=14.45; likuefaksi=12.57; gunungapi=0.0; karhutla=15.8 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -23877,25 +23898,25 @@
         <v>211.46</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>80</v>
+        <v>26.3</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>55</v>
+        <v>27.45</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>48</v>
+        <v>17.56</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>50</v>
+        <v>26.3</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>35</v>
+        <v>20.1</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>12</v>
+        <v>25.11</v>
       </c>
       <c r="O31" s="6" t="inlineStr"/>
       <c r="P31" s="6" t="inlineStr">
@@ -23905,7 +23926,7 @@
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=211.46 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=26.3 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=27.45 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=17.56; longsor=26.3; likuefaksi=20.1; gunungapi=0.0; karhutla=25.11 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -23952,25 +23973,25 @@
         <v>203.94</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>88</v>
+        <v>22.87</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>92</v>
+        <v>25.42</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>40</v>
+        <v>11.65</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>35</v>
+        <v>15.33</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>30</v>
+        <v>15.11</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>70</v>
+        <v>21.66</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>8</v>
+        <v>21.59</v>
       </c>
       <c r="O32" s="6" t="inlineStr"/>
       <c r="P32" s="6" t="inlineStr">
@@ -23980,7 +24001,7 @@
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=203.94 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=22.87 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=25.42 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=11.65; longsor=15.33; likuefaksi=15.11; gunungapi=21.66; karhutla=21.59 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -24027,25 +24048,25 @@
         <v>220.03</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>90</v>
+        <v>23.76</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>80</v>
+        <v>26.38</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>38</v>
+        <v>12.26</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>32</v>
+        <v>23.76</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>28</v>
+        <v>20.21</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>75</v>
+        <v>23.36</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>6</v>
+        <v>22.68</v>
       </c>
       <c r="O33" s="6" t="inlineStr"/>
       <c r="P33" s="6" t="inlineStr">
@@ -24055,7 +24076,7 @@
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=220.03 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=23.76 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=26.38 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=12.26; longsor=23.76; likuefaksi=20.21; gunungapi=23.36; karhutla=22.68 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -24102,25 +24123,25 @@
         <v>218.05</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>75</v>
+        <v>25.37</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>60</v>
+        <v>26.02</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>48</v>
+        <v>17.5</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>55</v>
+        <v>31.71</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>20</v>
+        <v>16.91</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>15</v>
+        <v>24.22</v>
       </c>
       <c r="O34" s="6" t="inlineStr"/>
       <c r="P34" s="6" t="inlineStr">
@@ -24130,7 +24151,7 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=218.05 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=25.37 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=26.02 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=17.5; longsor=31.71; likuefaksi=16.91; gunungapi=0.0; karhutla=24.22 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -24177,25 +24198,25 @@
         <v>218.51</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>70</v>
+        <v>24.68</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>75</v>
+        <v>25.27</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>42</v>
+        <v>17.07</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>40</v>
+        <v>25.6</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>18</v>
+        <v>17.34</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>12</v>
+        <v>24.44</v>
       </c>
       <c r="O35" s="6" t="inlineStr"/>
       <c r="P35" s="6" t="inlineStr">
@@ -24205,7 +24226,7 @@
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=218.51. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=24.68 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=25.27 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=17.07; longsor=25.6; likuefaksi=17.34; gunungapi=0.0; karhutla=24.44 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -24252,25 +24273,25 @@
         <v>165.4</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>55</v>
+        <v>16.6</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>30</v>
+        <v>1.6</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>58</v>
+        <v>17.6</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>45</v>
+        <v>12.38</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>12</v>
+        <v>15.49</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>18</v>
+        <v>25.2</v>
       </c>
       <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="6" t="inlineStr">
@@ -24280,7 +24301,7 @@
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=165.4. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=16.6 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=1.6 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=17.6; longsor=12.38; likuefaksi=15.49; gunungapi=0.0; karhutla=25.2 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -24327,25 +24348,25 @@
         <v>193.46</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>72</v>
+        <v>25.79</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>25</v>
+        <v>11.56</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>50</v>
+        <v>17.09</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>70</v>
+        <v>32.24</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>15</v>
+        <v>17.59</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>10</v>
+        <v>23.72</v>
       </c>
       <c r="O37" s="6" t="inlineStr"/>
       <c r="P37" s="6" t="inlineStr">
@@ -24355,7 +24376,7 @@
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=193.46 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=25.79 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=11.56 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=17.09; longsor=32.24; likuefaksi=17.59; gunungapi=0.0; karhutla=23.72 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -24402,25 +24423,25 @@
         <v>193.09</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>68</v>
+        <v>26.4</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>35</v>
+        <v>17.6</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>12</v>
+        <v>17.6</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>8</v>
+        <v>25.2</v>
       </c>
       <c r="O38" s="6" t="inlineStr"/>
       <c r="P38" s="6" t="inlineStr">
@@ -24430,7 +24451,7 @@
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=193.09 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=26.4 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=0.0 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=17.6; longsor=33.0; likuefaksi=17.6; gunungapi=0.0; karhutla=25.2 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -24477,25 +24498,25 @@
         <v>230.78</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>72</v>
+        <v>27.2</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>80</v>
+        <v>25.92</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>40</v>
+        <v>18.67</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>16</v>
+        <v>21.73</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>10</v>
+        <v>25.2</v>
       </c>
       <c r="O39" s="6" t="inlineStr"/>
       <c r="P39" s="6" t="inlineStr">
@@ -24505,7 +24526,7 @@
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>Komposit IRBI 2025=230.78 kelas Tinggi. Peta Bahaya dan Keselarasan memakai HANYA kolom komposit (opsi 1, 28 Agu 2026). Kolom per bahaya adalah sisa prototipe — tidak mewarnai peta.</t>
+          <t>Komposit IRBI 2025 resmi. Gempa=27.2 = rata-rata skor kabupaten IRBI 2025 gempabumi (buku hlm. 230–245, n kabupaten di provinsi ini). Bukan skor resmi provinsi BNPB. Filter peta masih mewarnai dari komposit saja. Tsunami=25.92 = rata-rata kab. IRBI 2025 tsunami (hlm. 248–256; kab tanpa paparan tidak di tabel = 0 untuk provinsi tanpa baris). banjir=18.67; longsor=27.5; likuefaksi=21.73; gunungapi=0.0; karhutla=25.2 (rata-rata kab. IRBI 2025; 0 = tidak ada baris di tabel ancaman itu).</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
